--- a/安全知识竞赛题库_标准化题库.xlsx
+++ b/安全知识竞赛题库_标准化题库.xlsx
@@ -54531,7 +54531,7 @@
         <v>3968</v>
       </c>
       <c r="B3" s="4">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16">
@@ -54547,7 +54547,7 @@
         <v>3970</v>
       </c>
       <c r="B5" s="4">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="16">
@@ -54571,7 +54571,7 @@
         <v>3973</v>
       </c>
       <c r="B8" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16">
@@ -54603,7 +54603,7 @@
         <v>20</v>
       </c>
       <c r="B12" s="4">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15">
